--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057567</t>
+          <t xml:space="preserve">200057570</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594594</t>
+          <t xml:space="preserve">311594599</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">

--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057570</t>
+          <t xml:space="preserve">200057567</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594599</t>
+          <t xml:space="preserve">311594594</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
